--- a/templates/approved/8. АОСР ВЛ1.xlsx
+++ b/templates/approved/8. АОСР ВЛ1.xlsx
@@ -4295,7 +4295,7 @@
       <c r="AI69" s="115"/>
       <c r="AJ69" s="115"/>
     </row>
-    <row r="70" spans="1:36" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:36" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="161" t="s">
         <v>171</v>
       </c>
@@ -9916,20 +9916,20 @@
       </c>
       <c r="B23" s="49"/>
       <c r="C23" s="50" t="str">
-        <f>IF(COUNTA(C2,C3)=0,"",CONCATENATE(C2,",",C3))</f>
+        <f>IF(AND(C2="",C3=""),"",CONCATENATE(IF(C2="","",C2),",",IF(C3="","",C3)))</f>
       </c>
       <c r="D23" s="50" t="str">
-        <f>IF(COUNTA(D2,D3)=0,"",CONCATENATE(D2,",",D3))</f>
+        <f>IF(AND(D2="",D3=""),"",CONCATENATE(IF(D2="","",D2),",",IF(D3="","",D3)))</f>
       </c>
       <c r="E23" s="51"/>
       <c r="G23" s="52" t="str">
-        <f>IF(COUNTA(G8,G1,G10,G9)=0,"",CONCATENATE(G8," ",G1,"-",G10," .",G9))</f>
+        <f>IF(AND(G8="",G1="",G10="",G9=""),"",CONCATENATE(IF(G8="","",G8)," ",IF(G1="","",G1),"-",IF(G10="","",G10)," .",IF(G9="","",G9)))</f>
       </c>
       <c r="H23" s="52" t="str">
-        <f>IF(COUNTA(H8,G1,H10,H9)=0,"",CONCATENATE(H8," ",G1,"-",H10,".",H9))</f>
+        <f>IF(AND(H8="",G1="",H10="",H9=""),"",CONCATENATE(IF(H8="","",H8)," ",IF(G1="","",G1),"-",IF(H10="","",H10),".",IF(H9="","",H9)))</f>
       </c>
       <c r="I23" s="52" t="str">
-        <f>IF(COUNTA(I8,G1,I10,I9)=0,"",CONCATENATE(I8," ",G1,"-",I10," .",I9))</f>
+        <f>IF(AND(I8="",G1="",I10="",I9=""),"",CONCATENATE(IF(I8="","",I8)," ",IF(G1="","",G1),"-",IF(I10="","",I10)," .",IF(I9="","",I9)))</f>
       </c>
     </row>
     <row r="24" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
@@ -9938,91 +9938,91 @@
       </c>
       <c r="B24" s="49"/>
       <c r="C24" s="50" t="str">
-        <f>IF(COUNTA(C1,C2,C3)=0,"",CONCATENATE(C1,",",C2,",",C3))</f>
+        <f>IF(AND(C1="",C2="",C3=""),"",CONCATENATE(IF(C1="","",C1),",",IF(C2="","",C2),",",IF(C3="","",C3)))</f>
       </c>
       <c r="D24" s="50" t="str">
-        <f>IF(COUNTA(D1,D2,D3)=0,"",CONCATENATE(D1,",",D2,",",D3))</f>
+        <f>IF(AND(D1="",D2="",D3=""),"",CONCATENATE(IF(D1="","",D1),",",IF(D2="","",D2),",",IF(D3="","",D3)))</f>
       </c>
       <c r="E24" s="51"/>
       <c r="G24" s="52" t="str">
-        <f>IF(COUNTA(G8,G1,G10)=0,"",CONCATENATE(G8," ",G1,"-",G10))</f>
+        <f>IF(AND(G8="",G1="",G10=""),"",CONCATENATE(IF(G8="","",G8)," ",IF(G1="","",G1),"-",IF(G10="","",G10)))</f>
       </c>
       <c r="H24" s="52" t="str">
-        <f>IF(COUNTA(H8,G1,H10)=0,"",CONCATENATE(H8," ",G1,"-",H10))</f>
+        <f>IF(AND(H8="",G1="",H10=""),"",CONCATENATE(IF(H8="","",H8)," ",IF(G1="","",G1),"-",IF(H10="","",H10)))</f>
       </c>
       <c r="I24" s="52" t="str">
-        <f>IF(COUNTA(I8,G1,I10)=0,"",CONCATENATE(I8," ",G1,"-",I10))</f>
+        <f>IF(AND(I8="",G1="",I10=""),"",CONCATENATE(IF(I8="","",I8)," ",IF(G1="","",G1),"-",IF(I10="","",I10)))</f>
       </c>
     </row>
     <row r="25" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="C25" s="53" t="str">
-        <f>IF(COUNTA(C8,C1,C10,C9)=0,"",CONCATENATE(C8," ",C1,"-",C10,".",C9))</f>
+        <f>IF(AND(C8="",C1="",C10="",C9=""),"",CONCATENATE(IF(C8="","",C8)," ",IF(C1="","",C1),"-",IF(C10="","",C10),".",IF(C9="","",C9)))</f>
       </c>
       <c r="D25" s="53" t="str">
-        <f>IF(COUNTA(D8,D1,D10,D9)=0,"",CONCATENATE(D8," ",D1,"-",D10,".",D9))</f>
+        <f>IF(AND(D8="",D1="",D10="",D9=""),"",CONCATENATE(IF(D8="","",D8)," ",IF(D1="","",D1),"-",IF(D10="","",D10),".",IF(D9="","",D9)))</f>
       </c>
       <c r="E25" s="54"/>
       <c r="G25" s="52" t="str">
-        <f>IF(COUNTA(G8,G1)=0,"",CONCATENATE(G8," ",G1))</f>
+        <f>IF(AND(G8="",G1=""),"",CONCATENATE(IF(G8="","",G8)," ",IF(G1="","",G1)))</f>
       </c>
       <c r="H25" s="52" t="str">
-        <f>IF(COUNTA(H8,G1)=0,"",CONCATENATE(H8," ",G1))</f>
+        <f>IF(AND(H8="",G1=""),"",CONCATENATE(IF(H8="","",H8)," ",IF(G1="","",G1)))</f>
       </c>
       <c r="I25" s="52" t="str">
-        <f>IF(COUNTA(I8,G1)=0,"",CONCATENATE(I8," ",G1))</f>
+        <f>IF(AND(I8="",G1=""),"",CONCATENATE(IF(I8="","",I8)," ",IF(G1="","",G1)))</f>
       </c>
     </row>
     <row r="26" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="C26" s="53" t="str">
-        <f>IF(COUNTA(C8,C1)=0,"",CONCATENATE(C8," ",C1))</f>
+        <f>IF(AND(C8="",C1=""),"",CONCATENATE(IF(C8="","",C8)," ",IF(C1="","",C1)))</f>
       </c>
       <c r="D26" s="53" t="str">
-        <f>IF(COUNTA(D8,D1)=0,"",CONCATENATE(D8," ",D1))</f>
+        <f>IF(AND(D8="",D1=""),"",CONCATENATE(IF(D8="","",D8)," ",IF(D1="","",D1)))</f>
       </c>
       <c r="E26" s="54"/>
       <c r="G26" s="49" t="str">
-        <f>IF(COUNTA(G6,G1,G7)=0,"",CONCATENATE(G6," ",G1," ",G7))</f>
+        <f>IF(AND(G6="",G1="",G7=""),"",CONCATENATE(IF(G6="","",G6)," ",IF(G1="","",G1)," ",IF(G7="","",G7)))</f>
       </c>
       <c r="H26" s="49"/>
       <c r="I26" s="49" t="str">
-        <f>IF(COUNTA(I6,G1,I7)=0,"",CONCATENATE(I6," ",G1," ",I7))</f>
+        <f>IF(AND(I6="",G1="",I7=""),"",CONCATENATE(IF(I6="","",I6)," ",IF(G1="","",G1)," ",IF(I7="","",I7)))</f>
       </c>
     </row>
     <row r="27" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="C27" s="55" t="str">
-        <f>IF(COUNTA(C18,C1,C20,C19)=0,"",CONCATENATE(C18," ",C1,"-",C20,".",C19))</f>
+        <f>IF(AND(C18="",C1="",C20="",C19=""),"",CONCATENATE(IF(C18="","",C18)," ",IF(C1="","",C1),"-",IF(C20="","",C20),".",IF(C19="","",C19)))</f>
       </c>
       <c r="D27" s="55" t="str">
-        <f>IF(COUNTA(D18,D1,D20,D19)=0,"",CONCATENATE(D18," ",D1,"-",D20,".",D19))</f>
+        <f>IF(AND(D18="",D1="",D20="",D19=""),"",CONCATENATE(IF(D18="","",D18)," ",IF(D1="","",D1),"-",IF(D20="","",D20),".",IF(D19="","",D19)))</f>
       </c>
       <c r="E27" s="52"/>
       <c r="G27" s="56" t="str">
-        <f>IF(COUNTA(G14,G1,G15)=0,"",CONCATENATE(G14," ",G1," ",G15))</f>
+        <f>IF(AND(G14="",G1="",G15=""),"",CONCATENATE(IF(G14="","",G14)," ",IF(G1="","",G1)," ",IF(G15="","",G15)))</f>
       </c>
       <c r="H27" s="56"/>
       <c r="I27" s="56" t="str">
-        <f>IF(COUNTA(I14,G1,I15)=0,"",CONCATENATE(I14," ",G1," ",I15))</f>
+        <f>IF(AND(I14="",G1="",I15=""),"",CONCATENATE(IF(I14="","",I14)," ",IF(G1="","",G1)," ",IF(I15="","",I15)))</f>
       </c>
     </row>
     <row r="28" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="C28" s="55" t="str">
-        <f>IF(COUNTA(C18,C1,C20)=0,"",CONCATENATE(C18," ",C1," ",C20))</f>
+        <f>IF(AND(C18="",C1="",C20=""),"",CONCATENATE(IF(C18="","",C18)," ",IF(C1="","",C1)," ",IF(C20="","",C20)))</f>
       </c>
       <c r="D28" s="55" t="str">
-        <f>IF(COUNTA(D18,D1,D20)=0,"",CONCATENATE(D18," ",D1,"-",D20))</f>
+        <f>IF(AND(D18="",D1="",D20=""),"",CONCATENATE(IF(D18="","",D18)," ",IF(D1="","",D1),"-",IF(D20="","",D20)))</f>
       </c>
       <c r="E28" s="52"/>
       <c r="G28" s="49" t="str">
-        <f>IF(COUNTA(G16,G1,G17)=0,"",CONCATENATE(G16," ",G1," ",G17))</f>
+        <f>IF(AND(G16="",G1="",G17=""),"",CONCATENATE(IF(G16="","",G16)," ",IF(G1="","",G1)," ",IF(G17="","",G17)))</f>
       </c>
       <c r="H28" s="49"/>
     </row>
     <row r="29" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="C29" s="57" t="str">
-        <f>IF(COUNTA(C18,C1)=0,"",CONCATENATE(C18," ",C1))</f>
+        <f>IF(AND(C18="",C1=""),"",CONCATENATE(IF(C18="","",C18)," ",IF(C1="","",C1)))</f>
       </c>
       <c r="D29" s="55" t="str">
-        <f>IF(COUNTA(D18,D1)=0,"",CONCATENATE(D18," ",D1))</f>
+        <f>IF(AND(D18="",D1=""),"",CONCATENATE(IF(D18="","",D18)," ",IF(D1="","",D1)))</f>
       </c>
       <c r="E29" s="52"/>
     </row>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="B11" s="71"/>
       <c r="C11" s="72" t="str">
-        <f>IF(COUNTA(B11,B12,B13)=0,"",CONCATENATE(B11," ",B12," ",B13))</f>
+        <f>IF(AND(B11="",B12="",B13=""),"",CONCATENATE(IF(B11="","",B11)," ",IF(B12="","",B12)," ",IF(B13="","",B13)))</f>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="B15" s="71"/>
       <c r="C15" s="72" t="str">
-        <f>IF(COUNTA(B14,B11,B15)=0,"",CONCATENATE(B14," ",B11," ",B15))</f>
+        <f>IF(AND(B14="",B11="",B15=""),"",CONCATENATE(IF(B14="","",B14)," ",IF(B11="","",B11)," ",IF(B15="","",B15)))</f>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="B16" s="71"/>
       <c r="C16" s="72" t="str">
-        <f>IF(COUNTA(B16,B11)=0,"",CONCATENATE(B16," ",B11))</f>
+        <f>IF(AND(B16="",B11=""),"",CONCATENATE(IF(B16="","",B16)," ",IF(B11="","",B11)))</f>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="B17" s="71"/>
       <c r="C17" s="73" t="str">
-        <f>IF(COUNTA(B16,B11,B17)=0,"",CONCATENATE(B16," ",B11," ",B17))</f>
+        <f>IF(AND(B16="",B11="",B17=""),"",CONCATENATE(IF(B16="","",B16)," ",IF(B11="","",B11)," ",IF(B17="","",B17)))</f>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="B18" s="71"/>
       <c r="C18" s="73" t="str">
-        <f>IF(COUNTA(B16,B11,B17,B18)=0,"",CONCATENATE(B16," ",B11," ",B17,".",B18))</f>
+        <f>IF(AND(B16="",B11="",B17="",B18=""),"",CONCATENATE(IF(B16="","",B16)," ",IF(B11="","",B11)," ",IF(B17="","",B17),".",IF(B18="","",B18)))</f>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="B19" s="71"/>
       <c r="C19" s="72" t="str">
-        <f>IF(COUNTA(B19,B11)=0,"",CONCATENATE(B19," ",B11))</f>
+        <f>IF(AND(B19="",B11=""),"",CONCATENATE(IF(B19="","",B19)," ",IF(B11="","",B11)))</f>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="B20" s="71"/>
       <c r="C20" s="73" t="str">
-        <f>IF(COUNTA(B19,B11,B20)=0,"",CONCATENATE(B19," ",B11," ",B20))</f>
+        <f>IF(AND(B19="",B11="",B20=""),"",CONCATENATE(IF(B19="","",B19)," ",IF(B11="","",B11)," ",IF(B20="","",B20)))</f>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="B21" s="71"/>
       <c r="C21" s="73" t="str">
-        <f>IF(COUNTA(B19,B11,B20,B21)=0,"",CONCATENATE(B19," ",B11," ",B20,".",B21))</f>
+        <f>IF(AND(B19="",B11="",B20="",B21=""),"",CONCATENATE(IF(B19="","",B19)," ",IF(B11="","",B11)," ",IF(B20="","",B20),".",IF(B21="","",B21)))</f>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="B23" s="75"/>
       <c r="C23" t="str">
-        <f>IF(COUNTA(B23,B24,B25)=0,"",CONCATENATE(B23," ",B24,",",B25))</f>
+        <f>IF(AND(B23="",B24="",B25=""),"",CONCATENATE(IF(B23="","",B23)," ",IF(B24="","",B24),",",IF(B25="","",B25)))</f>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="B26" s="76"/>
       <c r="C26" t="str">
-        <f>IF(COUNTA(B26,B23)=0,"",CONCATENATE(B26," ",B23))</f>
+        <f>IF(AND(B26="",B23=""),"",CONCATENATE(IF(B26="","",B26)," ",IF(B23="","",B23)))</f>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.25">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="B27" s="75"/>
       <c r="C27" t="str">
-        <f>IF(COUNTA(B26,B23,B27)=0,"",CONCATENATE(B26," ",B23," ",B27))</f>
+        <f>IF(AND(B26="",B23="",B27=""),"",CONCATENATE(IF(B26="","",B26)," ",IF(B23="","",B23)," ",IF(B27="","",B27)))</f>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.25">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="B28" s="75"/>
       <c r="C28" t="str">
-        <f>IF(COUNTA(B28,B23)=0,"",CONCATENATE(B28," ",B23))</f>
+        <f>IF(AND(B28="",B23=""),"",CONCATENATE(IF(B28="","",B28)," ",IF(B23="","",B23)))</f>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.25">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="B29" s="75"/>
       <c r="C29" t="str">
-        <f>IF(COUNTA(B28,B23,B29)=0,"",CONCATENATE(B28," ",B23," ",B29))</f>
+        <f>IF(AND(B28="",B23="",B29=""),"",CONCATENATE(IF(B28="","",B28)," ",IF(B23="","",B23)," ",IF(B29="","",B29)))</f>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.25">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="B30" s="75"/>
       <c r="C30" t="str">
-        <f>IF(COUNTA(B30,B23)=0,"",CONCATENATE(B30," ",B23))</f>
+        <f>IF(AND(B30="",B23=""),"",CONCATENATE(IF(B30="","",B30)," ",IF(B23="","",B23)))</f>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.25">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="B31" s="75"/>
       <c r="C31" t="str">
-        <f>IF(COUNTA(B30,B23,B31)=0,"",CONCATENATE(B30," ",B23," ",B31))</f>
+        <f>IF(AND(B30="",B23="",B31=""),"",CONCATENATE(IF(B30="","",B30)," ",IF(B23="","",B23)," ",IF(B31="","",B31)))</f>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="B32" s="75"/>
       <c r="C32" t="str">
-        <f>IF(COUNTA(B32,B23)=0,"",CONCATENATE(B32," ",B23))</f>
+        <f>IF(AND(B32="",B23=""),"",CONCATENATE(IF(B32="","",B32)," ",IF(B23="","",B23)))</f>
       </c>
     </row>
     <row r="33" spans="1:31" ht="15" x14ac:dyDescent="0.25">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="B33" s="75"/>
       <c r="C33" s="77" t="str">
-        <f>IF(COUNTA(B32,B23,B33)=0,"",CONCATENATE(B32," ",B23," ",B33))</f>
+        <f>IF(AND(B32="",B23="",B33=""),"",CONCATENATE(IF(B32="","",B32)," ",IF(B23="","",B23)," ",IF(B33="","",B33)))</f>
       </c>
     </row>
     <row r="34" spans="1:31" ht="15" x14ac:dyDescent="0.25">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="B34" s="93"/>
       <c r="C34" t="str">
-        <f>IF(COUNTA(B32,B23,B33,B34)=0,"",CONCATENATE(B32," ",B23," ",B33,", ",B34))</f>
+        <f>IF(AND(B32="",B23="",B33="",B34=""),"",CONCATENATE(IF(B32="","",B32)," ",IF(B23="","",B23)," ",IF(B33="","",B33),", ",IF(B34="","",B34)))</f>
       </c>
     </row>
     <row r="35" spans="1:31" ht="15" x14ac:dyDescent="0.25">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="B35" s="75"/>
       <c r="C35" t="str">
-        <f>IF(COUNTA(B35,B23)=0,"",CONCATENATE(B35," ",B23))</f>
+        <f>IF(AND(B35="",B23=""),"",CONCATENATE(IF(B35="","",B35)," ",IF(B23="","",B23)))</f>
       </c>
     </row>
     <row r="36" spans="1:31" ht="15" x14ac:dyDescent="0.25">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="B36" s="75"/>
       <c r="C36" s="77" t="str">
-        <f>IF(COUNTA(B35,B23,B36)=0,"",CONCATENATE(B35," ",B23," ",B36))</f>
+        <f>IF(AND(B35="",B23="",B36=""),"",CONCATENATE(IF(B35="","",B35)," ",IF(B23="","",B23)," ",IF(B36="","",B36)))</f>
       </c>
     </row>
     <row r="37" spans="1:31" ht="15" x14ac:dyDescent="0.25">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="B37" s="75"/>
       <c r="C37" t="str">
-        <f>IF(COUNTA(B35,B23,B36,B37)=0,"",CONCATENATE(B35," ",B23," ",B36,", ",B37))</f>
+        <f>IF(AND(B35="",B23="",B36="",B37=""),"",CONCATENATE(IF(B35="","",B35)," ",IF(B23="","",B23)," ",IF(B36="","",B36),", ",IF(B37="","",B37)))</f>
       </c>
     </row>
     <row r="38" spans="1:31" ht="14.25" x14ac:dyDescent="0.2">
@@ -18267,7 +18267,7 @@
       <c r="AI96" s="34"/>
       <c r="AJ96" s="34"/>
     </row>
-    <row r="97" spans="1:36" s="20" customFormat="1" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="34" t="s">
         <v>86</v>
       </c>
